--- a/exports/trend_1d/NMDC_full_report.xlsx
+++ b/exports/trend_1d/NMDC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42066</v>
+        <v>42067</v>
       </c>
       <c r="H2" t="n">
-        <v>16.7</v>
+        <v>15.95</v>
       </c>
       <c r="I2" t="n">
         <v>16.1256872759203</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" t="n">
-        <v>3.73</v>
+        <v>-0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>0.93</v>
+        <v>1.55</v>
       </c>
       <c r="M2" t="n">
         <v>1.74</v>
       </c>
       <c r="N2" t="n">
-        <v>4.26</v>
+        <v>4.49</v>
       </c>
       <c r="O2" t="n">
         <v>0.9399999999999999</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.62</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42249</v>
+        <v>42250</v>
       </c>
       <c r="H3" t="n">
-        <v>11.95</v>
+        <v>12.3</v>
       </c>
       <c r="I3" t="n">
         <v>12.29776243713709</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K3" t="n">
-        <v>25.08</v>
+        <v>22.88</v>
       </c>
       <c r="L3" t="n">
         <v>5.64</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.35</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42312</v>
+        <v>42313</v>
       </c>
       <c r="H4" t="n">
-        <v>11.35</v>
+        <v>11.25</v>
       </c>
       <c r="I4" t="n">
         <v>11.32169795739844</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.72</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>13.82</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>10.58</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42412.38541666666</v>
+        <v>42415.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>9.300000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="I5" t="n">
         <v>10.38618337231983</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>99.38541666666667</v>
+        <v>102.3854166666667</v>
       </c>
       <c r="K5" t="n">
-        <v>17.33</v>
+        <v>4.89</v>
       </c>
       <c r="L5" t="n">
         <v>2.67</v>
       </c>
       <c r="M5" t="n">
-        <v>2.72</v>
+        <v>9.68</v>
       </c>
       <c r="N5" t="n">
-        <v>5.52</v>
+        <v>15.05</v>
       </c>
       <c r="O5" t="n">
         <v>-0.88</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>18.97</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42423.38541666666</v>
+        <v>42424.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>11.15</v>
+        <v>9.6</v>
       </c>
       <c r="I6" t="n">
         <v>9.688039015872524</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>4.21</v>
+        <v>-10.28</v>
       </c>
       <c r="L6" t="n">
-        <v>8.41</v>
+        <v>11.21</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>12.11</v>
       </c>
       <c r="N6" t="n">
-        <v>0.47</v>
+        <v>13.9</v>
       </c>
       <c r="O6" t="n">
         <v>15.05</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>21.44</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42433.38541666666</v>
+        <v>42437.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>10.6</v>
+        <v>11.35</v>
       </c>
       <c r="I7" t="n">
         <v>11.29427009151743</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>-10.42</v>
+        <v>-18.23</v>
       </c>
       <c r="L7" t="n">
-        <v>11.98</v>
+        <v>23.44</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>4.72</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>7.08</v>
       </c>
       <c r="O7" t="n">
         <v>-13.9</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.88</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42493.38541666666</v>
+        <v>42494.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>11.6</v>
+        <v>11.15</v>
       </c>
       <c r="I8" t="n">
         <v>11.2553679119706</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2</v>
+        <v>-1.76</v>
       </c>
       <c r="L8" t="n">
         <v>4.41</v>
@@ -897,7 +992,7 @@
         <v>2.2</v>
       </c>
       <c r="N8" t="n">
-        <v>3.39</v>
+        <v>3.88</v>
       </c>
       <c r="O8" t="n">
         <v>7.08</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.43</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42551.38541666666</v>
+        <v>42552.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="I9" t="n">
         <v>11.2785564147298</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9</v>
+        <v>-1.35</v>
       </c>
       <c r="L9" t="n">
         <v>4.93</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>6.39</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42622.38541666666</v>
+        <v>42625.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>13.3</v>
+        <v>12.55</v>
       </c>
       <c r="I10" t="n">
         <v>12.57910144854429</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K10" t="n">
-        <v>17.7</v>
+        <v>11.06</v>
       </c>
       <c r="L10" t="n">
         <v>0.44</v>
       </c>
       <c r="M10" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>3.63</v>
+        <v>5.64</v>
       </c>
       <c r="O10" t="n">
         <v>0.44</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>12.25</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42648.38541666666</v>
+        <v>42649.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="I11" t="n">
         <v>13.54295286688818</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.77</v>
+        <v>-10.76</v>
       </c>
       <c r="L11" t="n">
-        <v>7.97</v>
+        <v>11.95</v>
       </c>
       <c r="M11" t="n">
         <v>1.5</v>
       </c>
       <c r="N11" t="n">
-        <v>3.67</v>
+        <v>3.73</v>
       </c>
       <c r="O11" t="n">
         <v>-5.64</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.64</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42685.38541666666</v>
+        <v>42689.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>15.15</v>
+        <v>14.2</v>
       </c>
       <c r="I12" t="n">
         <v>14.81546492763064</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K12" t="n">
-        <v>8.99</v>
+        <v>2.16</v>
       </c>
       <c r="L12" t="n">
         <v>2.16</v>
@@ -1125,7 +1268,7 @@
         <v>6.84</v>
       </c>
       <c r="N12" t="n">
-        <v>5.28</v>
+        <v>6.27</v>
       </c>
       <c r="O12" t="n">
         <v>3.73</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>20.87</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42738.38541666666</v>
+        <v>42739.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>15.7</v>
+        <v>16.2</v>
       </c>
       <c r="I13" t="n">
         <v>15.91813528594842</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" t="n">
-        <v>-10.56</v>
+        <v>-14.08</v>
       </c>
       <c r="L13" t="n">
-        <v>11.62</v>
+        <v>17.25</v>
       </c>
       <c r="M13" t="n">
         <v>2.86</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42815.38541666666</v>
+        <v>42816.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>16.55</v>
+        <v>16.1</v>
       </c>
       <c r="I14" t="n">
         <v>16.54091290518154</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K14" t="n">
-        <v>2.16</v>
+        <v>-0.62</v>
       </c>
       <c r="L14" t="n">
         <v>2.47</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42922.38541666666</v>
+        <v>42923.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>13.6</v>
+        <v>13.95</v>
       </c>
       <c r="I15" t="n">
         <v>13.61483412468223</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K15" t="n">
-        <v>15.53</v>
+        <v>13.35</v>
       </c>
       <c r="L15" t="n">
         <v>4.66</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.01</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42999.38541666666</v>
+        <v>43000.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>15.5</v>
+        <v>14.65</v>
       </c>
       <c r="I16" t="n">
         <v>14.92547798378889</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K16" t="n">
-        <v>11.11</v>
+        <v>5.02</v>
       </c>
       <c r="L16" t="n">
         <v>2.87</v>
@@ -1353,7 +1544,7 @@
         <v>2.39</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>5.48</v>
       </c>
       <c r="O16" t="n">
         <v>2.57</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>12.03</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43034.38541666666</v>
+        <v>43035.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>15.35</v>
+        <v>15.6</v>
       </c>
       <c r="I17" t="n">
         <v>15.42981073800599</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.78</v>
+        <v>-6.48</v>
       </c>
       <c r="L17" t="n">
-        <v>6.48</v>
+        <v>7.85</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7</v>
+        <v>0.98</v>
       </c>
       <c r="N17" t="n">
         <v>5.14</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.02</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43117.38541666666</v>
+        <v>43118.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>18.1</v>
+        <v>17.35</v>
       </c>
       <c r="I18" t="n">
         <v>17.74113600354322</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K18" t="n">
-        <v>16.03</v>
+        <v>11.22</v>
       </c>
       <c r="L18" t="n">
         <v>6.09</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>13.29</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43308.38541666666</v>
+        <v>43311.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>12.45</v>
+        <v>12.6</v>
       </c>
       <c r="I19" t="n">
         <v>12.57598236472874</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K19" t="n">
-        <v>28.24</v>
+        <v>27.38</v>
       </c>
       <c r="L19" t="n">
         <v>6.05</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43325.38541666666</v>
+        <v>43326.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>12.45</v>
+        <v>12.2</v>
       </c>
       <c r="I20" t="n">
         <v>12.2942534743877</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.19</v>
+        <v>-3.17</v>
       </c>
       <c r="L20" t="n">
-        <v>2.38</v>
+        <v>3.57</v>
       </c>
       <c r="M20" t="n">
         <v>3.3</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>13.69</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43348.38541666666</v>
+        <v>43349.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="I21" t="n">
         <v>13.65590751590881</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.84</v>
+        <v>-13.93</v>
       </c>
       <c r="L21" t="n">
-        <v>13.52</v>
+        <v>14.75</v>
       </c>
       <c r="M21" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="N21" t="n">
         <v>4.03</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>11.3</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43377.38541666666</v>
+        <v>43378.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>13.85</v>
+        <v>13.1</v>
       </c>
       <c r="I22" t="n">
         <v>13.33021393293514</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.36</v>
+        <v>-5.76</v>
       </c>
       <c r="L22" t="n">
-        <v>6.83</v>
+        <v>7.19</v>
       </c>
       <c r="M22" t="n">
         <v>1.67</v>
       </c>
       <c r="N22" t="n">
-        <v>4.56</v>
+        <v>5.42</v>
       </c>
       <c r="O22" t="n">
         <v>3.73</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>16.48</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43494</v>
+        <v>43495</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I23" t="n">
         <v>11.47822789029171</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>115.6145833333333</v>
+        <v>116.6145833333333</v>
       </c>
       <c r="K23" t="n">
-        <v>16.03</v>
+        <v>12.21</v>
       </c>
       <c r="L23" t="n">
         <v>8.779999999999999</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>9.25</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43544</v>
+        <v>43546</v>
       </c>
       <c r="H24" t="n">
-        <v>13.65</v>
+        <v>12.85</v>
       </c>
       <c r="I24" t="n">
         <v>13.13885452420782</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K24" t="n">
-        <v>18.7</v>
+        <v>11.74</v>
       </c>
       <c r="L24" t="n">
         <v>5.22</v>
       </c>
       <c r="M24" t="n">
-        <v>1.15</v>
+        <v>5.86</v>
       </c>
       <c r="N24" t="n">
-        <v>3.87</v>
+        <v>5.86</v>
       </c>
       <c r="O24" t="n">
         <v>4.55</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.58</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H25" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="I25" t="n">
         <v>11.76166702380508</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K25" t="n">
-        <v>8.949999999999999</v>
+        <v>5.06</v>
       </c>
       <c r="L25" t="n">
         <v>2.33</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.18</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H26" t="n">
-        <v>13.25</v>
+        <v>12.85</v>
       </c>
       <c r="I26" t="n">
         <v>13.02612574224328</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K26" t="n">
-        <v>8.609999999999999</v>
+        <v>5.33</v>
       </c>
       <c r="L26" t="n">
         <v>3.69</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>12.25</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43738</v>
+        <v>43739</v>
       </c>
       <c r="H27" t="n">
-        <v>10.55</v>
+        <v>11.55</v>
       </c>
       <c r="I27" t="n">
         <v>11.25973590041517</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K27" t="n">
-        <v>17.9</v>
+        <v>10.12</v>
       </c>
       <c r="L27" t="n">
         <v>10.12</v>
@@ -1980,7 +2303,7 @@
         <v>3.69</v>
       </c>
       <c r="N27" t="n">
-        <v>6.37</v>
+        <v>9.48</v>
       </c>
       <c r="O27" t="n">
         <v>-3.02</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>21.47</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43780</v>
+        <v>43782</v>
       </c>
       <c r="H28" t="n">
-        <v>12.45</v>
+        <v>12.05</v>
       </c>
       <c r="I28" t="n">
         <v>12.07812362993408</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K28" t="n">
-        <v>7.79</v>
+        <v>4.33</v>
       </c>
       <c r="L28" t="n">
         <v>10.39</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>17.22</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43802</v>
+        <v>43803</v>
       </c>
       <c r="H29" t="n">
-        <v>12.95</v>
+        <v>13.6</v>
       </c>
       <c r="I29" t="n">
         <v>13.31721965358943</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.47</v>
+        <v>-12.86</v>
       </c>
       <c r="L29" t="n">
-        <v>8.710000000000001</v>
+        <v>13.69</v>
       </c>
       <c r="M29" t="n">
         <v>0.84</v>
       </c>
       <c r="N29" t="n">
-        <v>3.77</v>
+        <v>5.02</v>
       </c>
       <c r="O29" t="n">
         <v>-3.21</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.04</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43838</v>
+        <v>43839</v>
       </c>
       <c r="H30" t="n">
-        <v>14.65</v>
+        <v>14.5</v>
       </c>
       <c r="I30" t="n">
         <v>14.51943410699538</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K30" t="n">
-        <v>7.72</v>
+        <v>6.62</v>
       </c>
       <c r="L30" t="n">
         <v>5.88</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>11.5</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43847</v>
+        <v>43850</v>
       </c>
       <c r="H31" t="n">
-        <v>15.6</v>
+        <v>16.75</v>
       </c>
       <c r="I31" t="n">
         <v>16.07607656874427</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.59</v>
+        <v>-15.52</v>
       </c>
       <c r="L31" t="n">
-        <v>10.34</v>
+        <v>15.86</v>
       </c>
       <c r="M31" t="n">
-        <v>1.71</v>
+        <v>3.85</v>
       </c>
       <c r="N31" t="n">
-        <v>4.29</v>
+        <v>7.37</v>
       </c>
       <c r="O31" t="n">
         <v>-1.02</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>11.63</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43858</v>
+        <v>43859</v>
       </c>
       <c r="H32" t="n">
-        <v>14.95</v>
+        <v>14.75</v>
       </c>
       <c r="I32" t="n">
         <v>14.80185386722998</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K32" t="n">
-        <v>-10.75</v>
+        <v>-11.94</v>
       </c>
       <c r="L32" t="n">
-        <v>11.94</v>
+        <v>12.84</v>
       </c>
       <c r="M32" t="n">
         <v>3.12</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>14.01</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H33" t="n">
-        <v>9.699999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="I33" t="n">
         <v>9.738416317912156</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K33" t="n">
-        <v>34.24</v>
+        <v>31.86</v>
       </c>
       <c r="L33" t="n">
         <v>2.71</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14.09</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H34" t="n">
-        <v>11.25</v>
+        <v>10.7</v>
       </c>
       <c r="I34" t="n">
         <v>11.12220201988393</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K34" t="n">
-        <v>11.94</v>
+        <v>6.47</v>
       </c>
       <c r="L34" t="n">
         <v>5.97</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>16.58</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44139</v>
+        <v>44140</v>
       </c>
       <c r="H35" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="I35" t="n">
         <v>10.47823691466475</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K35" t="n">
-        <v>4.67</v>
+        <v>-0.93</v>
       </c>
       <c r="L35" t="n">
         <v>6.07</v>
@@ -2436,7 +2855,7 @@
         <v>1.68</v>
       </c>
       <c r="N35" t="n">
-        <v>5.03</v>
+        <v>5.88</v>
       </c>
       <c r="O35" t="n">
         <v>-4.89</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.47</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44217</v>
+        <v>44218</v>
       </c>
       <c r="H36" t="n">
-        <v>14.1</v>
+        <v>13.45</v>
       </c>
       <c r="I36" t="n">
         <v>13.71131189799301</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K36" t="n">
-        <v>30.56</v>
+        <v>24.54</v>
       </c>
       <c r="L36" t="n">
         <v>5.56</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.91</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44249</v>
+        <v>44250</v>
       </c>
       <c r="H37" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="I37" t="n">
         <v>14.50328051676565</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.06</v>
+        <v>-10.04</v>
       </c>
       <c r="L37" t="n">
-        <v>10.78</v>
+        <v>12.64</v>
       </c>
       <c r="M37" t="n">
         <v>4.93</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.18</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44370</v>
+        <v>44371</v>
       </c>
       <c r="H38" t="n">
-        <v>21.65</v>
+        <v>21.3</v>
       </c>
       <c r="I38" t="n">
         <v>21.3322364517666</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K38" t="n">
-        <v>46.28</v>
+        <v>43.92</v>
       </c>
       <c r="L38" t="n">
         <v>2.7</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>13.61</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44477</v>
+        <v>44480</v>
       </c>
       <c r="H39" t="n">
-        <v>17.55</v>
+        <v>18.5</v>
       </c>
       <c r="I39" t="n">
         <v>18.25708147063275</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K39" t="n">
-        <v>17.61</v>
+        <v>13.15</v>
       </c>
       <c r="L39" t="n">
         <v>6.57</v>
@@ -2664,7 +3131,7 @@
         <v>2.4</v>
       </c>
       <c r="N39" t="n">
-        <v>5.35</v>
+        <v>5.41</v>
       </c>
       <c r="O39" t="n">
         <v>-1.62</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>12.56</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>16.95</v>
       </c>
       <c r="I40" t="n">
         <v>17.19304196209361</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
-        <v>-7.03</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>8.109999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M40" t="n">
         <v>-0</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.29</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44539</v>
+        <v>44540</v>
       </c>
       <c r="H41" t="n">
-        <v>17.75</v>
+        <v>17.9</v>
       </c>
       <c r="I41" t="n">
         <v>17.89294573426971</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.72</v>
+        <v>-5.6</v>
       </c>
       <c r="L41" t="n">
         <v>5.9</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>9.24</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44546</v>
+        <v>44547</v>
       </c>
       <c r="H42" t="n">
-        <v>16.45</v>
+        <v>16.25</v>
       </c>
       <c r="I42" t="n">
         <v>16.37942832645731</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>-8.1</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>8.94</v>
+        <v>9.5</v>
       </c>
       <c r="M42" t="n">
         <v>6.16</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>10.87</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44573</v>
+        <v>44574</v>
       </c>
       <c r="H43" t="n">
-        <v>17.05</v>
+        <v>17.6</v>
       </c>
       <c r="I43" t="n">
         <v>17.20606190941314</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.92</v>
+        <v>-8.31</v>
       </c>
       <c r="L43" t="n">
-        <v>5.54</v>
+        <v>8.92</v>
       </c>
       <c r="M43" t="n">
         <v>2.13</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.32</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H44" t="n">
-        <v>16.85</v>
+        <v>16.15</v>
       </c>
       <c r="I44" t="n">
         <v>16.21942789704112</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.26</v>
+        <v>-8.24</v>
       </c>
       <c r="L44" t="n">
-        <v>5.11</v>
+        <v>9.09</v>
       </c>
       <c r="M44" t="n">
         <v>0.57</v>
       </c>
       <c r="N44" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="O44" t="n">
         <v>3.23</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>11.21</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="H45" t="n">
-        <v>17.55</v>
+        <v>18.25</v>
       </c>
       <c r="I45" t="n">
         <v>17.80535258711454</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.67</v>
+        <v>-13</v>
       </c>
       <c r="L45" t="n">
-        <v>8.98</v>
+        <v>13.31</v>
       </c>
       <c r="M45" t="n">
         <v>1.54</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>11.29</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44608</v>
+        <v>44609</v>
       </c>
       <c r="H46" t="n">
-        <v>18.45</v>
+        <v>17.45</v>
       </c>
       <c r="I46" t="n">
         <v>17.57621277948846</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>1.1</v>
+        <v>-4.38</v>
       </c>
       <c r="L46" t="n">
         <v>4.93</v>
       </c>
       <c r="M46" t="n">
-        <v>1.31</v>
+        <v>2.98</v>
       </c>
       <c r="N46" t="n">
-        <v>3.66</v>
+        <v>5.42</v>
       </c>
       <c r="O46" t="n">
         <v>3.99</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>12.81</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44630</v>
+        <v>44631</v>
       </c>
       <c r="H47" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="I47" t="n">
         <v>18.59674711657753</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.02</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>8.31</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>3.7</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>11.75</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H48" t="n">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="I48" t="n">
         <v>19.32198913839834</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K48" t="n">
-        <v>6.32</v>
+        <v>1.05</v>
       </c>
       <c r="L48" t="n">
         <v>6.84</v>
       </c>
       <c r="M48" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="N48" t="n">
         <v>5.56</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>10.99</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44781</v>
+        <v>44783</v>
       </c>
       <c r="H49" t="n">
-        <v>13.55</v>
+        <v>13.95</v>
       </c>
       <c r="I49" t="n">
         <v>13.58895822956161</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K49" t="n">
-        <v>29.43</v>
+        <v>27.34</v>
       </c>
       <c r="L49" t="n">
         <v>3.65</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.07</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H50" t="n">
-        <v>32.9</v>
+        <v>31.35</v>
       </c>
       <c r="I50" t="n">
         <v>32.62222713843025</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K50" t="n">
-        <v>135.84</v>
+        <v>124.73</v>
       </c>
       <c r="L50" t="n">
         <v>3.94</v>
@@ -3291,7 +3890,7 @@
         <v>3.04</v>
       </c>
       <c r="N50" t="n">
-        <v>4.26</v>
+        <v>4.71</v>
       </c>
       <c r="O50" t="n">
         <v>2.95</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>12.03</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44925</v>
+        <v>44928</v>
       </c>
       <c r="H51" t="n">
-        <v>34.65</v>
+        <v>35.55</v>
       </c>
       <c r="I51" t="n">
         <v>35.12225686232549</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>-10.53</v>
+        <v>-13.4</v>
       </c>
       <c r="L51" t="n">
-        <v>11.16</v>
+        <v>13.72</v>
       </c>
       <c r="M51" t="n">
         <v>1.38</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44958</v>
+        <v>44959</v>
       </c>
       <c r="H52" t="n">
-        <v>34.05</v>
+        <v>33.7</v>
       </c>
       <c r="I52" t="n">
         <v>33.81197426854104</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.22</v>
+        <v>-5.2</v>
       </c>
       <c r="L52" t="n">
-        <v>5.91</v>
+        <v>6.47</v>
       </c>
       <c r="M52" t="n">
         <v>0.95</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45118</v>
+        <v>45119</v>
       </c>
       <c r="H53" t="n">
-        <v>31.35</v>
+        <v>32.4</v>
       </c>
       <c r="I53" t="n">
         <v>31.79863998573045</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K53" t="n">
-        <v>6.97</v>
+        <v>3.86</v>
       </c>
       <c r="L53" t="n">
         <v>3.41</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>6</v>
+      </c>
+      <c r="U53" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.44</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H54" t="n">
-        <v>69.89</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="I54" t="n">
         <v>68.14986332757876</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K54" t="n">
-        <v>115.71</v>
+        <v>98.27</v>
       </c>
       <c r="L54" t="n">
         <v>3.09</v>
@@ -3519,7 +4166,7 @@
         <v>1.59</v>
       </c>
       <c r="N54" t="n">
-        <v>5.56</v>
+        <v>8.08</v>
       </c>
       <c r="O54" t="n">
         <v>3.35</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>9</v>
+      </c>
+      <c r="U54" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>17.96</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45390</v>
+        <v>45391</v>
       </c>
       <c r="H55" t="n">
-        <v>70.06999999999999</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="I55" t="n">
         <v>70.38953419556344</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K55" t="n">
-        <v>-9.08</v>
+        <v>-10.97</v>
       </c>
       <c r="L55" t="n">
-        <v>9.619999999999999</v>
+        <v>11.53</v>
       </c>
       <c r="M55" t="n">
         <v>1.52</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.63</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H56" t="n">
-        <v>80.72</v>
+        <v>78</v>
       </c>
       <c r="I56" t="n">
         <v>79.72177288567323</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K56" t="n">
-        <v>13.23</v>
+        <v>9.41</v>
       </c>
       <c r="L56" t="n">
         <v>2.08</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>12.24</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="H57" t="n">
-        <v>70.59999999999999</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>70.82684914878072</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K57" t="n">
-        <v>9.49</v>
+        <v>6.08</v>
       </c>
       <c r="L57" t="n">
         <v>10.49</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>11.59</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45572</v>
+        <v>45573</v>
       </c>
       <c r="H58" t="n">
-        <v>71.53</v>
+        <v>68.48</v>
       </c>
       <c r="I58" t="n">
         <v>69.15816228321738</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.36</v>
+        <v>-6.52</v>
       </c>
       <c r="L58" t="n">
-        <v>5.3</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M58" t="n">
         <v>2.6</v>
       </c>
       <c r="N58" t="n">
-        <v>3.29</v>
+        <v>4.26</v>
       </c>
       <c r="O58" t="n">
         <v>3.77</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>12.36</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="H59" t="n">
-        <v>75.52</v>
+        <v>76.28</v>
       </c>
       <c r="I59" t="n">
         <v>75.63551862493316</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K59" t="n">
-        <v>-10.28</v>
+        <v>-11.39</v>
       </c>
       <c r="L59" t="n">
-        <v>12.44</v>
+        <v>13.46</v>
       </c>
       <c r="M59" t="n">
         <v>2.14</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.64</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="H60" t="n">
-        <v>72.75</v>
+        <v>71.14</v>
       </c>
       <c r="I60" t="n">
         <v>71.21721434958084</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.63</v>
+        <v>-6.74</v>
       </c>
       <c r="L60" t="n">
-        <v>6.04</v>
+        <v>6.95</v>
       </c>
       <c r="M60" t="n">
         <v>1.57</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H61" t="n">
-        <v>62.64</v>
+        <v>64.52</v>
       </c>
       <c r="I61" t="n">
         <v>63.8818738153085</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K61" t="n">
-        <v>11.95</v>
+        <v>9.31</v>
       </c>
       <c r="L61" t="n">
         <v>2.83</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>11.41</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H62" t="n">
-        <v>63.1</v>
+        <v>59.49</v>
       </c>
       <c r="I62" t="n">
         <v>61.76529218227714</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.2</v>
+        <v>-7.8</v>
       </c>
       <c r="L62" t="n">
-        <v>2.94</v>
+        <v>10.35</v>
       </c>
       <c r="M62" t="n">
-        <v>1.58</v>
+        <v>7.73</v>
       </c>
       <c r="N62" t="n">
         <v>7.68</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>13.14</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45790</v>
+        <v>45791</v>
       </c>
       <c r="H63" t="n">
-        <v>65.23</v>
+        <v>67.97</v>
       </c>
       <c r="I63" t="n">
         <v>66.82768429920797</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K63" t="n">
-        <v>-9.65</v>
+        <v>-14.25</v>
       </c>
       <c r="L63" t="n">
-        <v>12.72</v>
+        <v>14.93</v>
       </c>
       <c r="M63" t="n">
         <v>4.3</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>12.13</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="H64" t="n">
-        <v>68.43000000000001</v>
+        <v>66.61</v>
       </c>
       <c r="I64" t="n">
         <v>67.05976029319764</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K64" t="n">
-        <v>0.68</v>
+        <v>-2</v>
       </c>
       <c r="L64" t="n">
         <v>3.69</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45860</v>
+        <v>45861</v>
       </c>
       <c r="H65" t="n">
-        <v>70.01000000000001</v>
+        <v>70.83</v>
       </c>
       <c r="I65" t="n">
         <v>70.29775231984351</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K65" t="n">
-        <v>-5.1</v>
+        <v>-6.34</v>
       </c>
       <c r="L65" t="n">
-        <v>6.2</v>
+        <v>6.65</v>
       </c>
       <c r="M65" t="n">
         <v>1.85</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.87</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H66" t="n">
-        <v>71.34</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I66" t="n">
         <v>70.92884364168458</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K66" t="n">
-        <v>0.72</v>
+        <v>-0.61</v>
       </c>
       <c r="L66" t="n">
         <v>6.57</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.94</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="H67" t="n">
-        <v>73.09</v>
+        <v>75.64</v>
       </c>
       <c r="I67" t="n">
         <v>74.73768550120788</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.82</v>
+        <v>-7.44</v>
       </c>
       <c r="L67" t="n">
-        <v>6.34</v>
+        <v>7.6</v>
       </c>
       <c r="M67" t="n">
         <v>1.23</v>
       </c>
       <c r="N67" t="n">
-        <v>2.18</v>
+        <v>3.49</v>
       </c>
       <c r="O67" t="n">
         <v>-1.32</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.96</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H68" t="n">
-        <v>78.98999999999999</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="I68" t="n">
         <v>76.66857857339222</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K68" t="n">
-        <v>4.43</v>
+        <v>1.15</v>
       </c>
       <c r="L68" t="n">
         <v>3.13</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>10.96</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H69" t="n">
-        <v>79.23999999999999</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="I69" t="n">
         <v>82.29301318737443</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.57</v>
+        <v>-8.94</v>
       </c>
       <c r="L69" t="n">
-        <v>7.88</v>
+        <v>9.58</v>
       </c>
       <c r="M69" t="n">
         <v>3.01</v>
       </c>
       <c r="N69" t="n">
-        <v>3.78</v>
+        <v>5.19</v>
       </c>
       <c r="O69" t="n">
         <v>-3.14</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>13.83</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H70" t="n">
-        <v>79.78</v>
+        <v>75.09</v>
       </c>
       <c r="I70" t="n">
         <v>75.68575443556878</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.28</v>
+        <v>-9.91</v>
       </c>
       <c r="L70" t="n">
-        <v>8.82</v>
+        <v>10.56</v>
       </c>
       <c r="M70" t="n">
         <v>3.38</v>
       </c>
       <c r="N70" t="n">
-        <v>5.6</v>
+        <v>5.88</v>
       </c>
       <c r="O70" t="n">
         <v>5.19</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>13.73</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H71" t="n">
-        <v>84.44</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="I71" t="n">
         <v>84.8153069662259</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K71" t="n">
-        <v>-12.45</v>
+        <v>-13.29</v>
       </c>
       <c r="L71" t="n">
-        <v>13.2</v>
+        <v>14.93</v>
       </c>
       <c r="M71" t="n">
         <v>3.14</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>9.31</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="H72" t="n">
-        <v>88.19</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="I72" t="n">
         <v>86.96469556426155</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K72" t="n">
-        <v>3.67</v>
+        <v>0.22</v>
       </c>
       <c r="L72" t="n">
         <v>2.29</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>9.66</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="H73" t="n">
-        <v>85.94</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I73" t="n">
         <v>87.96312880342666</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.8</v>
+        <v>-3.46</v>
       </c>
       <c r="L73" t="n">
-        <v>3.41</v>
+        <v>4.27</v>
       </c>
       <c r="M73" t="n">
         <v>1.17</v>
       </c>
       <c r="N73" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="O73" t="n">
         <v>-3.32</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>4</v>
+      </c>
+      <c r="U73" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>7.71</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H74" t="n">
-        <v>82.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I74" t="n">
         <v>81.40662954081981</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.59</v>
+        <v>-8.74</v>
       </c>
       <c r="L74" t="n">
-        <v>6.76</v>
+        <v>8.74</v>
       </c>
       <c r="M74" t="n">
         <v>1.58</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>30</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9677,7 +10584,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.8</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="6">
@@ -9687,7 +10594,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -9697,7 +10604,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
@@ -9707,7 +10614,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9717,7 +10624,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -9727,7 +10634,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119.6</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="11">
@@ -9737,7 +10644,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -9747,7 +10654,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -9757,7 +10664,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.6</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="14">
@@ -9767,7 +10674,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.91</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -9777,7 +10684,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.24</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="16">
@@ -9787,7 +10694,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.46</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="17">
@@ -9797,7 +10704,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>135.84</v>
+        <v>124.73</v>
       </c>
     </row>
     <row r="18">
@@ -9807,7 +10714,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.1</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="19">
@@ -9817,7 +10724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.45</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="20">
@@ -9827,7 +10734,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.04</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="21">
@@ -9837,7 +10744,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.82</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="22">
@@ -9847,7 +10754,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -9857,7 +10764,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -9867,7 +10774,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="25">
@@ -9877,7 +10784,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.84</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="26">
@@ -9887,7 +10794,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.72</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="27">
@@ -9897,7 +10804,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.08</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="28">
@@ -9907,7 +10814,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
